--- a/tests/TC-10/results/timetable_all_departments_even.xlsx
+++ b/tests/TC-10/results/timetable_all_departments_even.xlsx
@@ -79,14 +79,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E0E0E0"/>
-        <bgColor rgb="00E0E0E0"/>
+        <fgColor rgb="00FFDAB3"/>
+        <bgColor rgb="00FFDAB3"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFDAB3"/>
-        <bgColor rgb="00FFDAB3"/>
+        <fgColor rgb="00E0E0E0"/>
+        <bgColor rgb="00E0E0E0"/>
       </patternFill>
     </fill>
     <fill>
@@ -178,14 +178,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -193,7 +193,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
@@ -817,12 +817,19 @@
       <c r="D2" s="8" t="inlineStr"/>
       <c r="E2" s="8" t="inlineStr"/>
       <c r="F2" s="8" t="inlineStr"/>
-      <c r="G2" s="8" t="inlineStr"/>
-      <c r="H2" s="8" t="inlineStr"/>
-      <c r="I2" s="8" t="inlineStr"/>
-      <c r="J2" s="8" t="inlineStr"/>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>CS202
+LEC
+Room: 101
+Dr. Math</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="n"/>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="11" t="n"/>
       <c r="K2" s="8" t="inlineStr"/>
-      <c r="L2" s="9" t="inlineStr">
+      <c r="L2" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -855,20 +862,13 @@
       <c r="C3" s="8" t="inlineStr"/>
       <c r="D3" s="8" t="inlineStr"/>
       <c r="E3" s="8" t="inlineStr"/>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>CS202
-LEC
-Room: 101
-Dr. Math</t>
-        </is>
-      </c>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="12" t="n"/>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="8" t="inlineStr"/>
+      <c r="H3" s="8" t="inlineStr"/>
+      <c r="I3" s="8" t="inlineStr"/>
       <c r="J3" s="8" t="inlineStr"/>
       <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="9" t="inlineStr">
+      <c r="L3" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -907,7 +907,7 @@
       <c r="I4" s="8" t="inlineStr"/>
       <c r="J4" s="8" t="inlineStr"/>
       <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="9" t="inlineStr">
+      <c r="L4" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -941,12 +941,19 @@
       <c r="D5" s="8" t="inlineStr"/>
       <c r="E5" s="8" t="inlineStr"/>
       <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="8" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr"/>
-      <c r="J5" s="8" t="inlineStr"/>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>CS202
+LEC
+Room: 101
+Dr. Math</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="n"/>
+      <c r="I5" s="10" t="n"/>
+      <c r="J5" s="11" t="n"/>
       <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="9" t="inlineStr">
+      <c r="L5" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -985,22 +992,15 @@
       <c r="I6" s="8" t="inlineStr"/>
       <c r="J6" s="8" t="inlineStr"/>
       <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="9" t="inlineStr">
+      <c r="L6" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
       <c r="M6" s="8" t="inlineStr"/>
-      <c r="N6" s="10" t="inlineStr">
-        <is>
-          <t>CS202
-LEC
-Room: 101
-Dr. Math</t>
-        </is>
-      </c>
-      <c r="O6" s="11" t="n"/>
-      <c r="P6" s="12" t="n"/>
+      <c r="N6" s="8" t="inlineStr"/>
+      <c r="O6" s="8" t="inlineStr"/>
+      <c r="P6" s="8" t="inlineStr"/>
       <c r="Q6" s="8" t="inlineStr"/>
       <c r="R6" s="8" t="inlineStr"/>
       <c r="S6" s="8" t="inlineStr"/>
@@ -1080,8 +1080,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="G2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1242,12 +1242,19 @@
       <c r="D2" s="8" t="inlineStr"/>
       <c r="E2" s="8" t="inlineStr"/>
       <c r="F2" s="8" t="inlineStr"/>
-      <c r="G2" s="8" t="inlineStr"/>
-      <c r="H2" s="8" t="inlineStr"/>
-      <c r="I2" s="8" t="inlineStr"/>
-      <c r="J2" s="8" t="inlineStr"/>
+      <c r="G2" s="9" t="inlineStr">
+        <is>
+          <t>CS202
+LEC
+Room: 101
+Dr. Math</t>
+        </is>
+      </c>
+      <c r="H2" s="10" t="n"/>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="11" t="n"/>
       <c r="K2" s="8" t="inlineStr"/>
-      <c r="L2" s="9" t="inlineStr">
+      <c r="L2" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -1280,20 +1287,13 @@
       <c r="C3" s="8" t="inlineStr"/>
       <c r="D3" s="8" t="inlineStr"/>
       <c r="E3" s="8" t="inlineStr"/>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>CS202
-LEC
-Room: 101
-Dr. Math</t>
-        </is>
-      </c>
-      <c r="G3" s="11" t="n"/>
-      <c r="H3" s="11" t="n"/>
-      <c r="I3" s="12" t="n"/>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="8" t="inlineStr"/>
+      <c r="H3" s="8" t="inlineStr"/>
+      <c r="I3" s="8" t="inlineStr"/>
       <c r="J3" s="8" t="inlineStr"/>
       <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="9" t="inlineStr">
+      <c r="L3" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -1332,7 +1332,7 @@
       <c r="I4" s="8" t="inlineStr"/>
       <c r="J4" s="8" t="inlineStr"/>
       <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="9" t="inlineStr">
+      <c r="L4" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -1366,12 +1366,19 @@
       <c r="D5" s="8" t="inlineStr"/>
       <c r="E5" s="8" t="inlineStr"/>
       <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="8" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr"/>
-      <c r="J5" s="8" t="inlineStr"/>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>CS202
+LEC
+Room: 101
+Dr. Math</t>
+        </is>
+      </c>
+      <c r="H5" s="10" t="n"/>
+      <c r="I5" s="10" t="n"/>
+      <c r="J5" s="11" t="n"/>
       <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="9" t="inlineStr">
+      <c r="L5" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -1410,22 +1417,15 @@
       <c r="I6" s="8" t="inlineStr"/>
       <c r="J6" s="8" t="inlineStr"/>
       <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="9" t="inlineStr">
+      <c r="L6" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
       </c>
       <c r="M6" s="8" t="inlineStr"/>
-      <c r="N6" s="10" t="inlineStr">
-        <is>
-          <t>CS202
-LEC
-Room: 101
-Dr. Math</t>
-        </is>
-      </c>
-      <c r="O6" s="11" t="n"/>
-      <c r="P6" s="12" t="n"/>
+      <c r="N6" s="8" t="inlineStr"/>
+      <c r="O6" s="8" t="inlineStr"/>
+      <c r="P6" s="8" t="inlineStr"/>
       <c r="Q6" s="8" t="inlineStr"/>
       <c r="R6" s="8" t="inlineStr"/>
       <c r="S6" s="8" t="inlineStr"/>
@@ -1505,8 +1505,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="F3:I3"/>
-    <mergeCell ref="N6:P6"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="G2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1672,7 +1672,7 @@
       <c r="I2" s="8" t="inlineStr"/>
       <c r="J2" s="8" t="inlineStr"/>
       <c r="K2" s="8" t="inlineStr"/>
-      <c r="L2" s="9" t="inlineStr">
+      <c r="L2" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -1704,22 +1704,7 @@
       </c>
       <c r="C3" s="8" t="inlineStr"/>
       <c r="D3" s="8" t="inlineStr"/>
-      <c r="E3" s="8" t="inlineStr"/>
-      <c r="F3" s="8" t="inlineStr"/>
-      <c r="G3" s="8" t="inlineStr"/>
-      <c r="H3" s="8" t="inlineStr"/>
-      <c r="I3" s="8" t="inlineStr"/>
-      <c r="J3" s="8" t="inlineStr"/>
-      <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="9" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M3" s="8" t="inlineStr"/>
-      <c r="N3" s="8" t="inlineStr"/>
-      <c r="O3" s="8" t="inlineStr"/>
-      <c r="P3" s="10" t="inlineStr">
+      <c r="E3" s="9" t="inlineStr">
         <is>
           <t>DS202
 LEC
@@ -1727,8 +1712,23 @@
 Dr. Math</t>
         </is>
       </c>
-      <c r="Q3" s="11" t="n"/>
-      <c r="R3" s="12" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="11" t="n"/>
+      <c r="I3" s="8" t="inlineStr"/>
+      <c r="J3" s="8" t="inlineStr"/>
+      <c r="K3" s="8" t="inlineStr"/>
+      <c r="L3" s="12" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M3" s="8" t="inlineStr"/>
+      <c r="N3" s="8" t="inlineStr"/>
+      <c r="O3" s="8" t="inlineStr"/>
+      <c r="P3" s="8" t="inlineStr"/>
+      <c r="Q3" s="8" t="inlineStr"/>
+      <c r="R3" s="8" t="inlineStr"/>
       <c r="S3" s="8" t="inlineStr"/>
       <c r="T3" s="8" t="inlineStr"/>
       <c r="U3" s="7" t="inlineStr">
@@ -1757,7 +1757,7 @@
       <c r="I4" s="8" t="inlineStr"/>
       <c r="J4" s="8" t="inlineStr"/>
       <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="9" t="inlineStr">
+      <c r="L4" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -1765,9 +1765,16 @@
       <c r="M4" s="8" t="inlineStr"/>
       <c r="N4" s="8" t="inlineStr"/>
       <c r="O4" s="8" t="inlineStr"/>
-      <c r="P4" s="8" t="inlineStr"/>
-      <c r="Q4" s="8" t="inlineStr"/>
-      <c r="R4" s="8" t="inlineStr"/>
+      <c r="P4" s="9" t="inlineStr">
+        <is>
+          <t>DS202
+LEC
+Room: 101
+Dr. Math</t>
+        </is>
+      </c>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="11" t="n"/>
       <c r="S4" s="8" t="inlineStr"/>
       <c r="T4" s="8" t="inlineStr"/>
       <c r="U4" s="7" t="inlineStr">
@@ -1796,7 +1803,7 @@
       <c r="I5" s="8" t="inlineStr"/>
       <c r="J5" s="8" t="inlineStr"/>
       <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="9" t="inlineStr">
+      <c r="L5" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -1830,19 +1837,12 @@
       <c r="D6" s="8" t="inlineStr"/>
       <c r="E6" s="8" t="inlineStr"/>
       <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>DS202
-LEC
-Room: 101
-Dr. Math</t>
-        </is>
-      </c>
-      <c r="H6" s="11" t="n"/>
-      <c r="I6" s="11" t="n"/>
-      <c r="J6" s="12" t="n"/>
+      <c r="G6" s="8" t="inlineStr"/>
+      <c r="H6" s="8" t="inlineStr"/>
+      <c r="I6" s="8" t="inlineStr"/>
+      <c r="J6" s="8" t="inlineStr"/>
       <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="9" t="inlineStr">
+      <c r="L6" s="12" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -1930,8 +1930,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="P3:R3"/>
+    <mergeCell ref="E3:H3"/>
+    <mergeCell ref="P4:R4"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1995,13 +1995,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2031,13 +2031,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -2067,13 +2067,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2103,13 +2103,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2142,10 +2142,10 @@
         <v>3</v>
       </c>
       <c r="C6" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2175,13 +2175,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>

--- a/tests/TC-10/results/timetable_all_departments_even.xlsx
+++ b/tests/TC-10/results/timetable_all_departments_even.xlsx
@@ -79,14 +79,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFDAB3"/>
-        <bgColor rgb="00FFDAB3"/>
+        <fgColor rgb="00E0E0E0"/>
+        <bgColor rgb="00E0E0E0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E0E0E0"/>
-        <bgColor rgb="00E0E0E0"/>
+        <fgColor rgb="00FFDAB3"/>
+        <bgColor rgb="00FFDAB3"/>
       </patternFill>
     </fill>
     <fill>
@@ -178,14 +178,14 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -193,7 +193,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
@@ -817,7 +817,20 @@
       <c r="D2" s="8" t="inlineStr"/>
       <c r="E2" s="8" t="inlineStr"/>
       <c r="F2" s="8" t="inlineStr"/>
-      <c r="G2" s="9" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr"/>
+      <c r="H2" s="8" t="inlineStr"/>
+      <c r="I2" s="8" t="inlineStr"/>
+      <c r="J2" s="8" t="inlineStr"/>
+      <c r="K2" s="8" t="inlineStr"/>
+      <c r="L2" s="9" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr"/>
+      <c r="N2" s="8" t="inlineStr"/>
+      <c r="O2" s="8" t="inlineStr"/>
+      <c r="P2" s="10" t="inlineStr">
         <is>
           <t>CS202
 LEC
@@ -825,21 +838,8 @@
 Dr. Math</t>
         </is>
       </c>
-      <c r="H2" s="10" t="n"/>
-      <c r="I2" s="10" t="n"/>
-      <c r="J2" s="11" t="n"/>
-      <c r="K2" s="8" t="inlineStr"/>
-      <c r="L2" s="12" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M2" s="8" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr"/>
-      <c r="O2" s="8" t="inlineStr"/>
-      <c r="P2" s="8" t="inlineStr"/>
-      <c r="Q2" s="8" t="inlineStr"/>
-      <c r="R2" s="8" t="inlineStr"/>
+      <c r="Q2" s="11" t="n"/>
+      <c r="R2" s="12" t="n"/>
       <c r="S2" s="8" t="inlineStr"/>
       <c r="T2" s="8" t="inlineStr"/>
       <c r="U2" s="7" t="inlineStr">
@@ -868,7 +868,7 @@
       <c r="I3" s="8" t="inlineStr"/>
       <c r="J3" s="8" t="inlineStr"/>
       <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="12" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -907,7 +907,7 @@
       <c r="I4" s="8" t="inlineStr"/>
       <c r="J4" s="8" t="inlineStr"/>
       <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="12" t="inlineStr">
+      <c r="L4" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -941,19 +941,12 @@
       <c r="D5" s="8" t="inlineStr"/>
       <c r="E5" s="8" t="inlineStr"/>
       <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>CS202
-LEC
-Room: 101
-Dr. Math</t>
-        </is>
-      </c>
-      <c r="H5" s="10" t="n"/>
-      <c r="I5" s="10" t="n"/>
-      <c r="J5" s="11" t="n"/>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
       <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="12" t="inlineStr">
+      <c r="L5" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -992,7 +985,7 @@
       <c r="I6" s="8" t="inlineStr"/>
       <c r="J6" s="8" t="inlineStr"/>
       <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="12" t="inlineStr">
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -1000,9 +993,16 @@
       <c r="M6" s="8" t="inlineStr"/>
       <c r="N6" s="8" t="inlineStr"/>
       <c r="O6" s="8" t="inlineStr"/>
-      <c r="P6" s="8" t="inlineStr"/>
-      <c r="Q6" s="8" t="inlineStr"/>
-      <c r="R6" s="8" t="inlineStr"/>
+      <c r="P6" s="10" t="inlineStr">
+        <is>
+          <t>CS202
+LEC
+Room: 101
+Dr. Math</t>
+        </is>
+      </c>
+      <c r="Q6" s="11" t="n"/>
+      <c r="R6" s="12" t="n"/>
       <c r="S6" s="8" t="inlineStr"/>
       <c r="T6" s="8" t="inlineStr"/>
       <c r="U6" s="7" t="inlineStr">
@@ -1080,8 +1080,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="P6:R6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1242,7 +1242,20 @@
       <c r="D2" s="8" t="inlineStr"/>
       <c r="E2" s="8" t="inlineStr"/>
       <c r="F2" s="8" t="inlineStr"/>
-      <c r="G2" s="9" t="inlineStr">
+      <c r="G2" s="8" t="inlineStr"/>
+      <c r="H2" s="8" t="inlineStr"/>
+      <c r="I2" s="8" t="inlineStr"/>
+      <c r="J2" s="8" t="inlineStr"/>
+      <c r="K2" s="8" t="inlineStr"/>
+      <c r="L2" s="9" t="inlineStr">
+        <is>
+          <t>LUNCH BREAK</t>
+        </is>
+      </c>
+      <c r="M2" s="8" t="inlineStr"/>
+      <c r="N2" s="8" t="inlineStr"/>
+      <c r="O2" s="8" t="inlineStr"/>
+      <c r="P2" s="10" t="inlineStr">
         <is>
           <t>CS202
 LEC
@@ -1250,21 +1263,8 @@
 Dr. Math</t>
         </is>
       </c>
-      <c r="H2" s="10" t="n"/>
-      <c r="I2" s="10" t="n"/>
-      <c r="J2" s="11" t="n"/>
-      <c r="K2" s="8" t="inlineStr"/>
-      <c r="L2" s="12" t="inlineStr">
-        <is>
-          <t>LUNCH BREAK</t>
-        </is>
-      </c>
-      <c r="M2" s="8" t="inlineStr"/>
-      <c r="N2" s="8" t="inlineStr"/>
-      <c r="O2" s="8" t="inlineStr"/>
-      <c r="P2" s="8" t="inlineStr"/>
-      <c r="Q2" s="8" t="inlineStr"/>
-      <c r="R2" s="8" t="inlineStr"/>
+      <c r="Q2" s="11" t="n"/>
+      <c r="R2" s="12" t="n"/>
       <c r="S2" s="8" t="inlineStr"/>
       <c r="T2" s="8" t="inlineStr"/>
       <c r="U2" s="7" t="inlineStr">
@@ -1293,7 +1293,7 @@
       <c r="I3" s="8" t="inlineStr"/>
       <c r="J3" s="8" t="inlineStr"/>
       <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="12" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -1332,7 +1332,7 @@
       <c r="I4" s="8" t="inlineStr"/>
       <c r="J4" s="8" t="inlineStr"/>
       <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="12" t="inlineStr">
+      <c r="L4" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -1366,19 +1366,12 @@
       <c r="D5" s="8" t="inlineStr"/>
       <c r="E5" s="8" t="inlineStr"/>
       <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="9" t="inlineStr">
-        <is>
-          <t>CS202
-LEC
-Room: 101
-Dr. Math</t>
-        </is>
-      </c>
-      <c r="H5" s="10" t="n"/>
-      <c r="I5" s="10" t="n"/>
-      <c r="J5" s="11" t="n"/>
+      <c r="G5" s="8" t="inlineStr"/>
+      <c r="H5" s="8" t="inlineStr"/>
+      <c r="I5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr"/>
       <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="12" t="inlineStr">
+      <c r="L5" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -1417,7 +1410,7 @@
       <c r="I6" s="8" t="inlineStr"/>
       <c r="J6" s="8" t="inlineStr"/>
       <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="12" t="inlineStr">
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -1425,9 +1418,16 @@
       <c r="M6" s="8" t="inlineStr"/>
       <c r="N6" s="8" t="inlineStr"/>
       <c r="O6" s="8" t="inlineStr"/>
-      <c r="P6" s="8" t="inlineStr"/>
-      <c r="Q6" s="8" t="inlineStr"/>
-      <c r="R6" s="8" t="inlineStr"/>
+      <c r="P6" s="10" t="inlineStr">
+        <is>
+          <t>CS202
+LEC
+Room: 101
+Dr. Math</t>
+        </is>
+      </c>
+      <c r="Q6" s="11" t="n"/>
+      <c r="R6" s="12" t="n"/>
       <c r="S6" s="8" t="inlineStr"/>
       <c r="T6" s="8" t="inlineStr"/>
       <c r="U6" s="7" t="inlineStr">
@@ -1505,8 +1505,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="G2:J2"/>
+    <mergeCell ref="P2:R2"/>
+    <mergeCell ref="P6:R6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1672,7 +1672,7 @@
       <c r="I2" s="8" t="inlineStr"/>
       <c r="J2" s="8" t="inlineStr"/>
       <c r="K2" s="8" t="inlineStr"/>
-      <c r="L2" s="12" t="inlineStr">
+      <c r="L2" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -1704,21 +1704,14 @@
       </c>
       <c r="C3" s="8" t="inlineStr"/>
       <c r="D3" s="8" t="inlineStr"/>
-      <c r="E3" s="9" t="inlineStr">
-        <is>
-          <t>DS202
-LEC
-Room: 101
-Dr. Math</t>
-        </is>
-      </c>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="11" t="n"/>
+      <c r="E3" s="8" t="inlineStr"/>
+      <c r="F3" s="8" t="inlineStr"/>
+      <c r="G3" s="8" t="inlineStr"/>
+      <c r="H3" s="8" t="inlineStr"/>
       <c r="I3" s="8" t="inlineStr"/>
       <c r="J3" s="8" t="inlineStr"/>
       <c r="K3" s="8" t="inlineStr"/>
-      <c r="L3" s="12" t="inlineStr">
+      <c r="L3" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -1757,7 +1750,7 @@
       <c r="I4" s="8" t="inlineStr"/>
       <c r="J4" s="8" t="inlineStr"/>
       <c r="K4" s="8" t="inlineStr"/>
-      <c r="L4" s="12" t="inlineStr">
+      <c r="L4" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -1765,7 +1758,32 @@
       <c r="M4" s="8" t="inlineStr"/>
       <c r="N4" s="8" t="inlineStr"/>
       <c r="O4" s="8" t="inlineStr"/>
-      <c r="P4" s="9" t="inlineStr">
+      <c r="P4" s="8" t="inlineStr"/>
+      <c r="Q4" s="8" t="inlineStr"/>
+      <c r="R4" s="8" t="inlineStr"/>
+      <c r="S4" s="8" t="inlineStr"/>
+      <c r="T4" s="8" t="inlineStr"/>
+      <c r="U4" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Thursday</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Minor Slot</t>
+        </is>
+      </c>
+      <c r="C5" s="8" t="inlineStr"/>
+      <c r="D5" s="8" t="inlineStr"/>
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>DS202
 LEC
@@ -1773,37 +1791,12 @@
 Dr. Math</t>
         </is>
       </c>
-      <c r="Q4" s="10" t="n"/>
-      <c r="R4" s="11" t="n"/>
-      <c r="S4" s="8" t="inlineStr"/>
-      <c r="T4" s="8" t="inlineStr"/>
-      <c r="U4" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Thursday</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Minor Slot</t>
-        </is>
-      </c>
-      <c r="C5" s="8" t="inlineStr"/>
-      <c r="D5" s="8" t="inlineStr"/>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="8" t="inlineStr"/>
-      <c r="H5" s="8" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr"/>
+      <c r="G5" s="11" t="n"/>
+      <c r="H5" s="11" t="n"/>
+      <c r="I5" s="12" t="n"/>
       <c r="J5" s="8" t="inlineStr"/>
       <c r="K5" s="8" t="inlineStr"/>
-      <c r="L5" s="12" t="inlineStr">
+      <c r="L5" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -1835,14 +1828,21 @@
       </c>
       <c r="C6" s="8" t="inlineStr"/>
       <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="8" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="8" t="inlineStr"/>
-      <c r="H6" s="8" t="inlineStr"/>
+      <c r="E6" s="10" t="inlineStr">
+        <is>
+          <t>DS202
+LEC
+Room: 101
+Dr. Math</t>
+        </is>
+      </c>
+      <c r="F6" s="11" t="n"/>
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="12" t="n"/>
       <c r="I6" s="8" t="inlineStr"/>
       <c r="J6" s="8" t="inlineStr"/>
       <c r="K6" s="8" t="inlineStr"/>
-      <c r="L6" s="12" t="inlineStr">
+      <c r="L6" s="9" t="inlineStr">
         <is>
           <t>LUNCH BREAK</t>
         </is>
@@ -1930,8 +1930,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="E3:H3"/>
-    <mergeCell ref="P4:R4"/>
+    <mergeCell ref="F5:I5"/>
+    <mergeCell ref="E6:H6"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1998,10 +1998,10 @@
         <v>2</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -2031,13 +2031,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -2070,10 +2070,10 @@
         <v>2</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -2103,13 +2103,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -2139,13 +2139,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -2175,13 +2175,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
